--- a/logs/experiments_not_systematic/sorted_by_experiment/1_head_comparison.xlsx
+++ b/logs/experiments_not_systematic/sorted_by_experiment/1_head_comparison.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/sorted_by_experiment/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/experiments_not_systematic/sorted_by_experiment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="11_AD4D2F04E46CFB4ACB3E20D455D6CCDA693EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D091741-953C-4584-B7FA-99D471698841}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="11_AD4D2F04E46CFB4ACB3E20D455D6CCDA693EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5CCEAC6-F48F-4F83-A7DA-F8F657A6E342}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5580" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main_experiments" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="1" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="155">
   <si>
     <t>date</t>
   </si>
@@ -421,9 +421,6 @@
   </si>
   <si>
     <t>effsu2</t>
-  </si>
-  <si>
-    <t>5</t>
   </si>
   <si>
     <t>[0, 1, 2, 3, 4, -1]</t>
@@ -664,7 +661,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -683,6 +680,9 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -779,10 +779,20 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="reps" numFmtId="0">
-      <sharedItems containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="5" maxValue="5"/>
+      <sharedItems containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="5" maxValue="5" count="5">
+        <s v="[3, 3, 2]"/>
+        <s v="[3, 3, 3, 2]"/>
+        <s v="5"/>
+        <s v="[3, 4]"/>
+        <n v="5"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="map" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="3">
+        <s v="[0, 1, 2]"/>
+        <s v="[0, 1, 2, 3, 4, -1]"/>
+        <s v="[[0, 1, 2], [0, 1, -1, 2, 3, -1]]"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="reorder" numFmtId="0">
       <sharedItems/>
@@ -1035,8 +1045,8 @@
     <s v="compact"/>
     <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
     <s v="full"/>
-    <s v="[3, 3, 2]"/>
-    <s v="[0, 1, 2]"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="false"/>
     <n v="190"/>
     <n v="70"/>
@@ -1132,8 +1142,8 @@
     <s v="compact"/>
     <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
     <s v="full"/>
-    <s v="[3, 3, 2]"/>
-    <s v="[0, 1, 2]"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="false"/>
     <n v="190"/>
     <n v="70"/>
@@ -1229,8 +1239,8 @@
     <s v="compact"/>
     <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
     <s v="full"/>
-    <s v="[3, 3, 2]"/>
-    <s v="[0, 1, 2]"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="false"/>
     <n v="190"/>
     <n v="70"/>
@@ -1326,8 +1336,8 @@
     <s v="compact"/>
     <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
     <s v="full"/>
-    <s v="[3, 3, 2]"/>
-    <s v="[0, 1, 2]"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="false"/>
     <n v="190"/>
     <n v="70"/>
@@ -1423,8 +1433,8 @@
     <s v="compact"/>
     <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
     <s v="full"/>
-    <s v="[3, 3, 2]"/>
-    <s v="[0, 1, 2]"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="false"/>
     <n v="190"/>
     <n v="70"/>
@@ -1520,8 +1530,8 @@
     <s v="compact"/>
     <s v="['effsu2', 'effsu2', 'effsu2', 'realamplitudes']"/>
     <s v="full"/>
-    <s v="[3, 3, 3, 2]"/>
-    <s v="[0, 1, 2]"/>
+    <x v="1"/>
+    <x v="0"/>
     <s v="false"/>
     <n v="220"/>
     <n v="100"/>
@@ -1617,8 +1627,8 @@
     <s v="compact"/>
     <s v="['effsu2', 'effsu2', 'effsu2', 'realamplitudes']"/>
     <s v="full"/>
-    <s v="[3, 3, 3, 2]"/>
-    <s v="[0, 1, 2]"/>
+    <x v="1"/>
+    <x v="0"/>
     <s v="false"/>
     <n v="220"/>
     <n v="100"/>
@@ -1714,8 +1724,8 @@
     <s v="compact"/>
     <s v="['effsu2', 'effsu2', 'effsu2', 'realamplitudes']"/>
     <s v="full"/>
-    <s v="[3, 3, 3, 2]"/>
-    <s v="[0, 1, 2]"/>
+    <x v="1"/>
+    <x v="0"/>
     <s v="false"/>
     <n v="220"/>
     <n v="100"/>
@@ -1811,8 +1821,8 @@
     <s v="compact"/>
     <s v="effsu2"/>
     <s v="full"/>
-    <s v="5"/>
-    <s v="[0, 1, 2, 3, 4, -1]"/>
+    <x v="2"/>
+    <x v="1"/>
     <s v="false"/>
     <n v="170"/>
     <n v="50"/>
@@ -1908,8 +1918,8 @@
     <s v="compact"/>
     <s v="effsu2"/>
     <s v="full"/>
-    <s v="[3, 4]"/>
-    <s v="[[0, 1, 2], [0, 1, -1, 2, 3, -1]]"/>
+    <x v="3"/>
+    <x v="2"/>
     <s v="false"/>
     <n v="190"/>
     <n v="70"/>
@@ -2005,8 +2015,8 @@
     <s v="compact"/>
     <s v="effsu2"/>
     <s v="full"/>
-    <s v="[3, 4]"/>
-    <s v="[[0, 1, 2], [0, 1, -1, 2, 3, -1]]"/>
+    <x v="3"/>
+    <x v="2"/>
     <s v="false"/>
     <n v="190"/>
     <n v="70"/>
@@ -2102,8 +2112,8 @@
     <s v="compact"/>
     <s v="effsu2"/>
     <s v="full"/>
-    <s v="5"/>
-    <s v="[0, 1, 2, 3, 4, -1]"/>
+    <x v="2"/>
+    <x v="1"/>
     <s v="false"/>
     <n v="170"/>
     <n v="50"/>
@@ -2199,8 +2209,8 @@
     <s v="compact"/>
     <s v="effsu2"/>
     <s v="full"/>
-    <s v="[3, 4]"/>
-    <s v="[[0, 1, 2], [0, 1, -1, 2, 3, -1]]"/>
+    <x v="3"/>
+    <x v="2"/>
     <s v="false"/>
     <n v="190"/>
     <n v="70"/>
@@ -2296,8 +2306,8 @@
     <s v="compact"/>
     <s v="effsu2"/>
     <s v="full"/>
-    <s v="5"/>
-    <s v="[0, 1, 2, 3, 4, -1]"/>
+    <x v="2"/>
+    <x v="1"/>
     <s v="false"/>
     <n v="170"/>
     <n v="50"/>
@@ -2393,8 +2403,8 @@
     <s v="compact"/>
     <s v="effsu2"/>
     <s v="full"/>
-    <s v="[3, 4]"/>
-    <s v="[[0, 1, 2], [0, 1, -1, 2, 3, -1]]"/>
+    <x v="3"/>
+    <x v="2"/>
     <s v="false"/>
     <n v="190"/>
     <n v="70"/>
@@ -2490,8 +2500,8 @@
     <s v="compact"/>
     <s v="effsu2"/>
     <s v="full"/>
-    <s v="[3, 4]"/>
-    <s v="[[0, 1, 2], [0, 1, -1, 2, 3, -1]]"/>
+    <x v="3"/>
+    <x v="2"/>
     <s v="false"/>
     <n v="190"/>
     <n v="70"/>
@@ -2587,8 +2597,8 @@
     <s v="compact"/>
     <s v="effsu2"/>
     <s v="full"/>
-    <n v="5"/>
-    <s v="[0, 1, 2, 3, 4, -1]"/>
+    <x v="4"/>
+    <x v="1"/>
     <s v="false"/>
     <n v="170"/>
     <n v="50"/>
@@ -2684,8 +2694,8 @@
     <s v="compact"/>
     <s v="effsu2"/>
     <s v="full"/>
-    <s v="5"/>
-    <s v="[0, 1, 2, 3, 4, -1]"/>
+    <x v="2"/>
+    <x v="1"/>
     <s v="false"/>
     <n v="170"/>
     <n v="50"/>
@@ -2781,8 +2791,8 @@
     <s v="compact"/>
     <s v="['effsu2', 'effsu2', 'effsu2', 'realamplitudes']"/>
     <s v="full"/>
-    <s v="[3, 3, 3, 2]"/>
-    <s v="[0, 1, 2]"/>
+    <x v="1"/>
+    <x v="0"/>
     <s v="false"/>
     <n v="220"/>
     <n v="100"/>
@@ -2878,8 +2888,8 @@
     <s v="compact"/>
     <s v="['effsu2', 'effsu2', 'effsu2', 'realamplitudes']"/>
     <s v="full"/>
-    <s v="[3, 3, 3, 2]"/>
-    <s v="[0, 1, 2]"/>
+    <x v="1"/>
+    <x v="0"/>
     <s v="false"/>
     <n v="220"/>
     <n v="100"/>
@@ -2958,8 +2968,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6E077427-C516-4EB5-9747-E7A1FFB2538F}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A1:G6" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6E077427-C516-4EB5-9747-E7A1FFB2538F}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A1:G10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="95">
     <pivotField numFmtId="164" showAll="0"/>
     <pivotField showAll="0"/>
@@ -2988,18 +2998,34 @@
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="5">
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item sd="0" x="2"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -3074,22 +3100,35 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
-  <rowFields count="2">
+  <rowFields count="3">
     <field x="16"/>
+    <field x="21"/>
     <field x="2"/>
   </rowFields>
-  <rowItems count="5">
+  <rowItems count="9">
     <i>
       <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
     </i>
     <i>
       <x v="1"/>
     </i>
+    <i r="1">
+      <x/>
+    </i>
     <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
       <x v="2"/>
     </i>
     <i>
       <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
     </i>
     <i t="grand">
       <x/>
@@ -6041,11 +6080,11 @@
       <c r="T10" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="U10" s="3" t="s">
+      <c r="U10" s="3">
+        <v>5</v>
+      </c>
+      <c r="V10" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="V10" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="W10" s="3" t="s">
         <v>101</v>
@@ -6270,7 +6309,7 @@
         <v>46058.144548611112</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C11" s="5">
         <v>2</v>
@@ -6285,7 +6324,7 @@
         <v>4.5</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>98</v>
@@ -6312,7 +6351,7 @@
         <v>102</v>
       </c>
       <c r="P11" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q11" s="5" t="str">
         <f t="shared" si="0"/>
@@ -6328,10 +6367,10 @@
         <v>106</v>
       </c>
       <c r="U11" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="V11" s="5" t="s">
         <v>131</v>
-      </c>
-      <c r="V11" s="5" t="s">
-        <v>132</v>
       </c>
       <c r="W11" s="5" t="s">
         <v>101</v>
@@ -6556,7 +6595,7 @@
         <v>46057.570532407408</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C12" s="3">
         <v>0</v>
@@ -6571,7 +6610,7 @@
         <v>4.5</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>98</v>
@@ -6598,7 +6637,7 @@
         <v>102</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q12" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6614,10 +6653,10 @@
         <v>106</v>
       </c>
       <c r="U12" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="V12" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="W12" s="3" t="s">
         <v>101</v>
@@ -6842,7 +6881,7 @@
         <v>46057.771296296298</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C13" s="5">
         <v>2</v>
@@ -6899,11 +6938,11 @@
       <c r="T13" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="U13" s="5" t="s">
+      <c r="U13" s="5">
+        <v>5</v>
+      </c>
+      <c r="V13" s="5" t="s">
         <v>126</v>
-      </c>
-      <c r="V13" s="5" t="s">
-        <v>127</v>
       </c>
       <c r="W13" s="5" t="s">
         <v>101</v>
@@ -7128,7 +7167,7 @@
         <v>46058.023113425923</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C14" s="3">
         <v>1</v>
@@ -7143,7 +7182,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>98</v>
@@ -7170,7 +7209,7 @@
         <v>102</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q14" s="3" t="str">
         <f t="shared" si="0"/>
@@ -7186,10 +7225,10 @@
         <v>106</v>
       </c>
       <c r="U14" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="V14" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>101</v>
@@ -7414,7 +7453,7 @@
         <v>46057.840775462973</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C15" s="5">
         <v>3</v>
@@ -7471,11 +7510,11 @@
       <c r="T15" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="U15" s="5" t="s">
+      <c r="U15" s="5">
+        <v>5</v>
+      </c>
+      <c r="V15" s="5" t="s">
         <v>126</v>
-      </c>
-      <c r="V15" s="5" t="s">
-        <v>127</v>
       </c>
       <c r="W15" s="5" t="s">
         <v>101</v>
@@ -7700,7 +7739,7 @@
         <v>46058.26803240741</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C16" s="3">
         <v>3</v>
@@ -7715,7 +7754,7 @@
         <v>4.5</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>98</v>
@@ -7742,7 +7781,7 @@
         <v>102</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q16" s="3" t="str">
         <f t="shared" si="0"/>
@@ -7758,10 +7797,10 @@
         <v>106</v>
       </c>
       <c r="U16" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="V16" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="V16" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="W16" s="3" t="s">
         <v>101</v>
@@ -7986,7 +8025,7 @@
         <v>46058.394270833327</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C17" s="5">
         <v>4</v>
@@ -8001,7 +8040,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>98</v>
@@ -8028,7 +8067,7 @@
         <v>102</v>
       </c>
       <c r="P17" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q17" s="5" t="str">
         <f t="shared" si="0"/>
@@ -8044,10 +8083,10 @@
         <v>106</v>
       </c>
       <c r="U17" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="V17" s="5" t="s">
         <v>131</v>
-      </c>
-      <c r="V17" s="5" t="s">
-        <v>132</v>
       </c>
       <c r="W17" s="5" t="s">
         <v>101</v>
@@ -8272,7 +8311,7 @@
         <v>46057.492997685193</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C18" s="3">
         <v>0</v>
@@ -8333,7 +8372,7 @@
         <v>5</v>
       </c>
       <c r="V18" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="W18" s="3" t="s">
         <v>101</v>
@@ -8558,7 +8597,7 @@
         <v>46057.680347222216</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C19" s="7">
         <v>1</v>
@@ -8615,11 +8654,11 @@
       <c r="T19" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="U19" s="7" t="s">
+      <c r="U19" s="7">
+        <v>5</v>
+      </c>
+      <c r="V19" s="7" t="s">
         <v>126</v>
-      </c>
-      <c r="V19" s="7" t="s">
-        <v>127</v>
       </c>
       <c r="W19" s="7" t="s">
         <v>101</v>
@@ -8844,7 +8883,7 @@
         <v>46062.393159722233</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C20" s="5">
         <v>1</v>
@@ -8886,10 +8925,10 @@
         <v>102</v>
       </c>
       <c r="P20" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q20" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="R20" s="5" t="s">
         <v>104</v>
@@ -9129,7 +9168,7 @@
         <v>46062.594837962963</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C21" s="12">
         <v>3</v>
@@ -9171,10 +9210,10 @@
         <v>102</v>
       </c>
       <c r="P21" s="12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q21" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="R21" s="12" t="s">
         <v>104</v>
@@ -9416,10 +9455,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2C275CB-F391-4B0D-A4B8-5C6BD94C729E}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="37.88671875" bestFit="1" customWidth="1"/>
@@ -9430,139 +9469,231 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C1" t="s">
         <v>147</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>148</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>149</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>150</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>151</v>
-      </c>
-      <c r="G1" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="B2" s="14">
+        <v>141</v>
+      </c>
+      <c r="B2" s="15">
         <v>0.22038340928464736</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="15">
         <v>-4.7112631465773921E-2</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="15">
         <v>5.5054504672610603E-2</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="15">
         <v>0.20850753798992999</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="15">
         <v>8.6877911818315084E-2</v>
       </c>
-      <c r="G2" s="14">
+      <c r="G2" s="15">
         <v>0.53109368265773393</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="B3" s="14">
-        <v>0.23858311042276811</v>
-      </c>
-      <c r="C3" s="14">
-        <v>-9.5641494910481656E-2</v>
-      </c>
-      <c r="D3" s="14">
-        <v>0.62652392472593077</v>
-      </c>
-      <c r="E3" s="14">
-        <v>9.4152336196548614E-2</v>
-      </c>
-      <c r="F3" s="14">
-        <v>0.20053558760922305</v>
-      </c>
-      <c r="G3" s="14">
-        <v>3.312059315936855E-2</v>
+      <c r="A3" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3" s="15">
+        <v>0.22038340928464736</v>
+      </c>
+      <c r="C3" s="15">
+        <v>-4.7112631465773921E-2</v>
+      </c>
+      <c r="D3" s="15">
+        <v>5.5054504672610603E-2</v>
+      </c>
+      <c r="E3" s="15">
+        <v>0.20850753798992999</v>
+      </c>
+      <c r="F3" s="15">
+        <v>8.6877911818315084E-2</v>
+      </c>
+      <c r="G3" s="15">
+        <v>0.53109368265773393</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="B4" s="14">
-        <v>0.62567560138709766</v>
-      </c>
-      <c r="C4" s="14">
-        <v>-4.0692606709303594E-2</v>
-      </c>
-      <c r="D4" s="14">
-        <v>0.61688549098113898</v>
-      </c>
-      <c r="E4" s="14">
-        <v>0.76469790189610998</v>
-      </c>
-      <c r="F4" s="14">
-        <v>0.46764533123144669</v>
-      </c>
-      <c r="G4" s="14">
-        <v>0.65347368143969631</v>
+        <v>142</v>
+      </c>
+      <c r="B4" s="15">
+        <v>0.23858311042276811</v>
+      </c>
+      <c r="C4" s="15">
+        <v>-9.5641494910481656E-2</v>
+      </c>
+      <c r="D4" s="15">
+        <v>0.62652392472593077</v>
+      </c>
+      <c r="E4" s="15">
+        <v>9.4152336196548614E-2</v>
+      </c>
+      <c r="F4" s="15">
+        <v>0.20053558760922305</v>
+      </c>
+      <c r="G4" s="15">
+        <v>3.312059315936855E-2</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="B5" s="14">
-        <v>0.56927524672700813</v>
-      </c>
-      <c r="C5" s="14">
-        <v>-0.2212015854558726</v>
-      </c>
-      <c r="D5" s="14">
-        <v>0.59955003749177938</v>
-      </c>
-      <c r="E5" s="14">
-        <v>0.68423000684429047</v>
-      </c>
-      <c r="F5" s="14">
-        <v>0.34470859513842017</v>
-      </c>
-      <c r="G5" s="14">
-        <v>0.64861234743354257</v>
+      <c r="A5" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="B5" s="15">
+        <v>0.23858311042276811</v>
+      </c>
+      <c r="C5" s="15">
+        <v>-9.5641494910481656E-2</v>
+      </c>
+      <c r="D5" s="15">
+        <v>0.62652392472593077</v>
+      </c>
+      <c r="E5" s="15">
+        <v>9.4152336196548614E-2</v>
+      </c>
+      <c r="F5" s="15">
+        <v>0.20053558760922305</v>
+      </c>
+      <c r="G5" s="15">
+        <v>3.312059315936855E-2</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="B6" s="14">
+        <v>143</v>
+      </c>
+      <c r="B6" s="15">
+        <v>0.62567560138709766</v>
+      </c>
+      <c r="C6" s="15">
+        <v>-4.0692606709303594E-2</v>
+      </c>
+      <c r="D6" s="15">
+        <v>0.61688549098113898</v>
+      </c>
+      <c r="E6" s="15">
+        <v>0.76469790189610998</v>
+      </c>
+      <c r="F6" s="15">
+        <v>0.46764533123144669</v>
+      </c>
+      <c r="G6" s="15">
+        <v>0.65347368143969631</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="15">
+        <v>0.62567560138709766</v>
+      </c>
+      <c r="C7" s="15">
+        <v>-4.0692606709303594E-2</v>
+      </c>
+      <c r="D7" s="15">
+        <v>0.61688549098113898</v>
+      </c>
+      <c r="E7" s="15">
+        <v>0.76469790189610998</v>
+      </c>
+      <c r="F7" s="15">
+        <v>0.46764533123144669</v>
+      </c>
+      <c r="G7" s="15">
+        <v>0.65347368143969631</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="B8" s="15">
+        <v>0.56927524672700813</v>
+      </c>
+      <c r="C8" s="15">
+        <v>-0.2212015854558726</v>
+      </c>
+      <c r="D8" s="15">
+        <v>0.59955003749177938</v>
+      </c>
+      <c r="E8" s="15">
+        <v>0.68423000684429047</v>
+      </c>
+      <c r="F8" s="15">
+        <v>0.34470859513842017</v>
+      </c>
+      <c r="G8" s="15">
+        <v>0.64861234743354257</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="15">
+        <v>0.56927524672700813</v>
+      </c>
+      <c r="C9" s="15">
+        <v>-0.2212015854558726</v>
+      </c>
+      <c r="D9" s="15">
+        <v>0.59955003749177938</v>
+      </c>
+      <c r="E9" s="15">
+        <v>0.68423000684429047</v>
+      </c>
+      <c r="F9" s="15">
+        <v>0.34470859513842017</v>
+      </c>
+      <c r="G9" s="15">
+        <v>0.64861234743354257</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="B10" s="15">
         <v>0.41347934195538028</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C10" s="15">
         <v>-0.10116207963535795</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D10" s="15">
         <v>0.47450348946786491</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E10" s="15">
         <v>0.43789694573171972</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F10" s="15">
         <v>0.27494185644935126</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G10" s="15">
         <v>0.46657507617258542</v>
       </c>
     </row>
